--- a/wwwroot/57/ExtrasCalculation.xlsx
+++ b/wwwroot/57/ExtrasCalculation.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="778" uniqueCount="778">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="779" uniqueCount="779">
   <si>
     <t>SubjectName</t>
   </si>
@@ -2342,10 +2342,13 @@
     <t>University Extra</t>
   </si>
   <si>
-    <t>40</t>
+    <t>50</t>
   </si>
   <si>
     <t>100000</t>
+  </si>
+  <si>
+    <t>3</t>
   </si>
 </sst>
 </file>
@@ -20572,10 +20575,10 @@
         <v>22</v>
       </c>
       <c r="L443" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
       <c r="M443" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
     </row>
     <row r="444">
@@ -20613,10 +20616,10 @@
         <v>22</v>
       </c>
       <c r="L444" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
       <c r="M444" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
     </row>
     <row r="445">
@@ -20654,10 +20657,10 @@
         <v>22</v>
       </c>
       <c r="L445" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
       <c r="M445" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
     </row>
     <row r="446">
@@ -20695,10 +20698,10 @@
         <v>22</v>
       </c>
       <c r="L446" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
       <c r="M446" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
     </row>
     <row r="447">
@@ -20736,10 +20739,10 @@
         <v>22</v>
       </c>
       <c r="L447" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
       <c r="M447" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
     </row>
     <row r="448">
@@ -20777,10 +20780,10 @@
         <v>22</v>
       </c>
       <c r="L448" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
       <c r="M448" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
     </row>
     <row r="449">
@@ -20818,10 +20821,10 @@
         <v>22</v>
       </c>
       <c r="L449" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
       <c r="M449" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
     </row>
     <row r="450">
@@ -20859,10 +20862,10 @@
         <v>22</v>
       </c>
       <c r="L450" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
       <c r="M450" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
     </row>
     <row r="451">
@@ -20900,10 +20903,10 @@
         <v>22</v>
       </c>
       <c r="L451" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
       <c r="M451" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
     </row>
     <row r="452">
@@ -20941,10 +20944,10 @@
         <v>22</v>
       </c>
       <c r="L452" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
       <c r="M452" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
     </row>
     <row r="453">
@@ -20982,10 +20985,10 @@
         <v>22</v>
       </c>
       <c r="L453" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
       <c r="M453" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
     </row>
     <row r="454">
@@ -21023,10 +21026,10 @@
         <v>22</v>
       </c>
       <c r="L454" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
       <c r="M454" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
     </row>
     <row r="455">
@@ -21064,10 +21067,10 @@
         <v>22</v>
       </c>
       <c r="L455" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
       <c r="M455" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
     </row>
     <row r="456">
@@ -21105,10 +21108,10 @@
         <v>22</v>
       </c>
       <c r="L456" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
       <c r="M456" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
     </row>
     <row r="457">
@@ -21146,10 +21149,10 @@
         <v>22</v>
       </c>
       <c r="L457" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
       <c r="M457" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
     </row>
     <row r="458">
@@ -21187,10 +21190,10 @@
         <v>22</v>
       </c>
       <c r="L458" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
       <c r="M458" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
     </row>
     <row r="459">
@@ -21228,10 +21231,10 @@
         <v>22</v>
       </c>
       <c r="L459" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
       <c r="M459" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
     </row>
     <row r="460">
@@ -21269,10 +21272,10 @@
         <v>22</v>
       </c>
       <c r="L460" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
       <c r="M460" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
     </row>
     <row r="461">
@@ -21310,10 +21313,10 @@
         <v>22</v>
       </c>
       <c r="L461" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
       <c r="M461" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
     </row>
     <row r="462">
@@ -21351,10 +21354,10 @@
         <v>22</v>
       </c>
       <c r="L462" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
       <c r="M462" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
     </row>
     <row r="463">
@@ -21392,10 +21395,10 @@
         <v>22</v>
       </c>
       <c r="L463" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
       <c r="M463" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
     </row>
     <row r="464">
@@ -21433,10 +21436,10 @@
         <v>22</v>
       </c>
       <c r="L464" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
       <c r="M464" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
     </row>
     <row r="465">
@@ -21474,10 +21477,10 @@
         <v>22</v>
       </c>
       <c r="L465" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
       <c r="M465" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
     </row>
     <row r="466">
@@ -21515,10 +21518,10 @@
         <v>22</v>
       </c>
       <c r="L466" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
       <c r="M466" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
     </row>
     <row r="467">
@@ -21556,10 +21559,10 @@
         <v>22</v>
       </c>
       <c r="L467" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
       <c r="M467" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
     </row>
     <row r="468">
@@ -21597,10 +21600,10 @@
         <v>22</v>
       </c>
       <c r="L468" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
       <c r="M468" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
     </row>
     <row r="469">
@@ -21638,10 +21641,10 @@
         <v>22</v>
       </c>
       <c r="L469" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
       <c r="M469" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
     </row>
     <row r="470">
@@ -21679,10 +21682,10 @@
         <v>22</v>
       </c>
       <c r="L470" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
       <c r="M470" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
     </row>
     <row r="471">
@@ -21720,10 +21723,10 @@
         <v>22</v>
       </c>
       <c r="L471" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
       <c r="M471" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
     </row>
     <row r="472">
@@ -21761,10 +21764,10 @@
         <v>22</v>
       </c>
       <c r="L472" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
       <c r="M472" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
     </row>
     <row r="473">
@@ -21802,10 +21805,10 @@
         <v>22</v>
       </c>
       <c r="L473" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
       <c r="M473" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
     </row>
     <row r="474">
@@ -21843,10 +21846,10 @@
         <v>22</v>
       </c>
       <c r="L474" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
       <c r="M474" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
     </row>
     <row r="475">
@@ -21884,10 +21887,10 @@
         <v>22</v>
       </c>
       <c r="L475" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
       <c r="M475" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
     </row>
     <row r="476">
@@ -21925,10 +21928,10 @@
         <v>22</v>
       </c>
       <c r="L476" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
       <c r="M476" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
     </row>
     <row r="477">
@@ -21966,10 +21969,10 @@
         <v>22</v>
       </c>
       <c r="L477" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
       <c r="M477" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
     </row>
     <row r="478">
@@ -22007,10 +22010,10 @@
         <v>22</v>
       </c>
       <c r="L478" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
       <c r="M478" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
     </row>
     <row r="479">
@@ -22048,10 +22051,10 @@
         <v>22</v>
       </c>
       <c r="L479" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
       <c r="M479" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
     </row>
     <row r="480">
@@ -22089,10 +22092,10 @@
         <v>22</v>
       </c>
       <c r="L480" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
       <c r="M480" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
     </row>
     <row r="481">
@@ -22130,10 +22133,10 @@
         <v>22</v>
       </c>
       <c r="L481" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
       <c r="M481" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
     </row>
     <row r="482">
@@ -22171,10 +22174,10 @@
         <v>22</v>
       </c>
       <c r="L482" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
       <c r="M482" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
     </row>
     <row r="483">
@@ -22212,10 +22215,10 @@
         <v>22</v>
       </c>
       <c r="L483" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
       <c r="M483" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
     </row>
     <row r="484">
@@ -22253,10 +22256,10 @@
         <v>22</v>
       </c>
       <c r="L484" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
       <c r="M484" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
     </row>
     <row r="485">
@@ -22294,10 +22297,10 @@
         <v>22</v>
       </c>
       <c r="L485" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
       <c r="M485" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
     </row>
     <row r="486">
@@ -22335,10 +22338,10 @@
         <v>22</v>
       </c>
       <c r="L486" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
       <c r="M486" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
     </row>
     <row r="487">
@@ -22376,10 +22379,10 @@
         <v>22</v>
       </c>
       <c r="L487" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
       <c r="M487" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
     </row>
     <row r="488">
@@ -22417,10 +22420,10 @@
         <v>22</v>
       </c>
       <c r="L488" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
       <c r="M488" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
     </row>
     <row r="489">
@@ -22458,10 +22461,10 @@
         <v>22</v>
       </c>
       <c r="L489" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
       <c r="M489" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
     </row>
     <row r="490">
@@ -22499,10 +22502,10 @@
         <v>22</v>
       </c>
       <c r="L490" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
       <c r="M490" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
     </row>
     <row r="491">
@@ -22540,10 +22543,10 @@
         <v>22</v>
       </c>
       <c r="L491" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
       <c r="M491" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
     </row>
     <row r="492">
@@ -22581,10 +22584,10 @@
         <v>22</v>
       </c>
       <c r="L492" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
       <c r="M492" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
     </row>
     <row r="493">
@@ -22622,10 +22625,10 @@
         <v>22</v>
       </c>
       <c r="L493" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
       <c r="M493" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
     </row>
     <row r="494">
@@ -22663,10 +22666,10 @@
         <v>22</v>
       </c>
       <c r="L494" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
       <c r="M494" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
     </row>
     <row r="495">
@@ -22704,10 +22707,10 @@
         <v>22</v>
       </c>
       <c r="L495" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
       <c r="M495" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
     </row>
     <row r="496">
@@ -22745,10 +22748,10 @@
         <v>22</v>
       </c>
       <c r="L496" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
       <c r="M496" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
     </row>
     <row r="497">
@@ -22786,10 +22789,10 @@
         <v>22</v>
       </c>
       <c r="L497" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
       <c r="M497" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
     </row>
     <row r="498">
@@ -22827,10 +22830,10 @@
         <v>22</v>
       </c>
       <c r="L498" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
       <c r="M498" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
     </row>
     <row r="499">
@@ -22868,10 +22871,10 @@
         <v>22</v>
       </c>
       <c r="L499" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
       <c r="M499" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
     </row>
     <row r="500">
@@ -22909,10 +22912,10 @@
         <v>22</v>
       </c>
       <c r="L500" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
       <c r="M500" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
     </row>
     <row r="501">
@@ -22950,10 +22953,10 @@
         <v>22</v>
       </c>
       <c r="L501" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
       <c r="M501" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
     </row>
     <row r="502">
@@ -22991,10 +22994,10 @@
         <v>22</v>
       </c>
       <c r="L502" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
       <c r="M502" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
     </row>
     <row r="503">
@@ -23032,10 +23035,10 @@
         <v>22</v>
       </c>
       <c r="L503" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
       <c r="M503" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
     </row>
     <row r="504">
@@ -23073,10 +23076,10 @@
         <v>22</v>
       </c>
       <c r="L504" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
       <c r="M504" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
     </row>
     <row r="505">
@@ -23114,10 +23117,10 @@
         <v>22</v>
       </c>
       <c r="L505" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
       <c r="M505" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
     </row>
     <row r="506">
@@ -23155,10 +23158,10 @@
         <v>22</v>
       </c>
       <c r="L506" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
       <c r="M506" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
     </row>
     <row r="507">
@@ -23196,10 +23199,10 @@
         <v>22</v>
       </c>
       <c r="L507" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
       <c r="M507" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
     </row>
     <row r="508">
@@ -23237,10 +23240,10 @@
         <v>22</v>
       </c>
       <c r="L508" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
       <c r="M508" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
     </row>
     <row r="509">
@@ -23278,10 +23281,10 @@
         <v>22</v>
       </c>
       <c r="L509" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
       <c r="M509" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
     </row>
     <row r="510">
@@ -23319,10 +23322,10 @@
         <v>22</v>
       </c>
       <c r="L510" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
       <c r="M510" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
     </row>
     <row r="511">
@@ -23360,10 +23363,10 @@
         <v>22</v>
       </c>
       <c r="L511" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
       <c r="M511" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
     </row>
     <row r="512">
@@ -23401,10 +23404,10 @@
         <v>22</v>
       </c>
       <c r="L512" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
       <c r="M512" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
     </row>
     <row r="513">
@@ -23442,10 +23445,10 @@
         <v>22</v>
       </c>
       <c r="L513" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
       <c r="M513" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
     </row>
     <row r="514">
@@ -23483,10 +23486,10 @@
         <v>22</v>
       </c>
       <c r="L514" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
       <c r="M514" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
     </row>
     <row r="515">
@@ -23524,10 +23527,10 @@
         <v>22</v>
       </c>
       <c r="L515" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
       <c r="M515" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
     </row>
     <row r="516">
@@ -23565,10 +23568,10 @@
         <v>22</v>
       </c>
       <c r="L516" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
       <c r="M516" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
     </row>
     <row r="517">
@@ -23606,10 +23609,10 @@
         <v>22</v>
       </c>
       <c r="L517" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
       <c r="M517" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
     </row>
     <row r="518">
@@ -23647,10 +23650,10 @@
         <v>22</v>
       </c>
       <c r="L518" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
       <c r="M518" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
     </row>
     <row r="519">
@@ -23688,10 +23691,10 @@
         <v>22</v>
       </c>
       <c r="L519" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
       <c r="M519" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
     </row>
     <row r="520">
@@ -23729,10 +23732,10 @@
         <v>22</v>
       </c>
       <c r="L520" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
       <c r="M520" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
     </row>
     <row r="521">
@@ -23770,10 +23773,10 @@
         <v>22</v>
       </c>
       <c r="L521" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
       <c r="M521" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
     </row>
     <row r="522">
@@ -23811,10 +23814,10 @@
         <v>22</v>
       </c>
       <c r="L522" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
       <c r="M522" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
     </row>
     <row r="523">
@@ -23852,10 +23855,10 @@
         <v>22</v>
       </c>
       <c r="L523" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
       <c r="M523" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
     </row>
     <row r="524">
@@ -23893,10 +23896,10 @@
         <v>22</v>
       </c>
       <c r="L524" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
       <c r="M524" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
     </row>
     <row r="525">
@@ -23934,10 +23937,10 @@
         <v>22</v>
       </c>
       <c r="L525" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
       <c r="M525" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
     </row>
     <row r="526">
@@ -23975,10 +23978,10 @@
         <v>22</v>
       </c>
       <c r="L526" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
       <c r="M526" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
     </row>
     <row r="527">
@@ -24016,10 +24019,10 @@
         <v>22</v>
       </c>
       <c r="L527" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
       <c r="M527" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
     </row>
     <row r="528">
@@ -24057,10 +24060,10 @@
         <v>22</v>
       </c>
       <c r="L528" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
       <c r="M528" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
     </row>
     <row r="529">
@@ -24098,10 +24101,10 @@
         <v>22</v>
       </c>
       <c r="L529" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
       <c r="M529" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
     </row>
     <row r="530">
@@ -24139,10 +24142,10 @@
         <v>22</v>
       </c>
       <c r="L530" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
       <c r="M530" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
     </row>
     <row r="531">
@@ -24180,10 +24183,10 @@
         <v>22</v>
       </c>
       <c r="L531" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
       <c r="M531" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
     </row>
     <row r="532">
@@ -24221,10 +24224,10 @@
         <v>22</v>
       </c>
       <c r="L532" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
       <c r="M532" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
     </row>
     <row r="533">
@@ -24262,10 +24265,10 @@
         <v>22</v>
       </c>
       <c r="L533" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
       <c r="M533" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
     </row>
     <row r="534">
@@ -24303,10 +24306,10 @@
         <v>22</v>
       </c>
       <c r="L534" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
       <c r="M534" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
     </row>
     <row r="535">
@@ -24344,10 +24347,10 @@
         <v>22</v>
       </c>
       <c r="L535" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
       <c r="M535" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
     </row>
     <row r="536">
@@ -24385,10 +24388,10 @@
         <v>22</v>
       </c>
       <c r="L536" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
       <c r="M536" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
     </row>
     <row r="537">
@@ -24426,10 +24429,10 @@
         <v>22</v>
       </c>
       <c r="L537" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
       <c r="M537" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
     </row>
     <row r="538">
@@ -24467,10 +24470,10 @@
         <v>22</v>
       </c>
       <c r="L538" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
       <c r="M538" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
     </row>
     <row r="539">
@@ -24508,10 +24511,10 @@
         <v>22</v>
       </c>
       <c r="L539" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
       <c r="M539" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
     </row>
     <row r="540">
@@ -24549,10 +24552,10 @@
         <v>22</v>
       </c>
       <c r="L540" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
       <c r="M540" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
     </row>
     <row r="541">
@@ -24590,10 +24593,10 @@
         <v>22</v>
       </c>
       <c r="L541" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
       <c r="M541" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
     </row>
     <row r="542">
@@ -24631,10 +24634,10 @@
         <v>22</v>
       </c>
       <c r="L542" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
       <c r="M542" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
     </row>
     <row r="543">
@@ -24672,10 +24675,10 @@
         <v>22</v>
       </c>
       <c r="L543" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
       <c r="M543" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
     </row>
     <row r="544">
@@ -24713,10 +24716,10 @@
         <v>22</v>
       </c>
       <c r="L544" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
       <c r="M544" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
     </row>
     <row r="545">
@@ -24754,10 +24757,10 @@
         <v>22</v>
       </c>
       <c r="L545" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
       <c r="M545" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
     </row>
     <row r="546">
@@ -24795,10 +24798,10 @@
         <v>22</v>
       </c>
       <c r="L546" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
       <c r="M546" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
     </row>
     <row r="547">
@@ -24836,10 +24839,10 @@
         <v>22</v>
       </c>
       <c r="L547" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
       <c r="M547" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
     </row>
     <row r="548">
@@ -24877,10 +24880,10 @@
         <v>22</v>
       </c>
       <c r="L548" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
       <c r="M548" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
     </row>
     <row r="549">
@@ -24918,10 +24921,10 @@
         <v>22</v>
       </c>
       <c r="L549" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
       <c r="M549" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
     </row>
     <row r="550">
@@ -24959,10 +24962,10 @@
         <v>22</v>
       </c>
       <c r="L550" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
       <c r="M550" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
     </row>
     <row r="551">
@@ -25000,10 +25003,10 @@
         <v>22</v>
       </c>
       <c r="L551" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
       <c r="M551" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
     </row>
     <row r="552">
@@ -25041,10 +25044,10 @@
         <v>22</v>
       </c>
       <c r="L552" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
       <c r="M552" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
     </row>
     <row r="553">
@@ -25082,10 +25085,10 @@
         <v>22</v>
       </c>
       <c r="L553" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
       <c r="M553" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
     </row>
     <row r="554">
@@ -25123,10 +25126,10 @@
         <v>22</v>
       </c>
       <c r="L554" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
       <c r="M554" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
     </row>
     <row r="555">
@@ -25164,10 +25167,10 @@
         <v>22</v>
       </c>
       <c r="L555" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
       <c r="M555" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
     </row>
     <row r="556">
@@ -25205,10 +25208,10 @@
         <v>22</v>
       </c>
       <c r="L556" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
       <c r="M556" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
     </row>
     <row r="557">
@@ -25246,10 +25249,10 @@
         <v>22</v>
       </c>
       <c r="L557" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
       <c r="M557" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
     </row>
     <row r="558">
@@ -25287,10 +25290,10 @@
         <v>22</v>
       </c>
       <c r="L558" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
       <c r="M558" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
     </row>
     <row r="559">
@@ -25328,10 +25331,10 @@
         <v>22</v>
       </c>
       <c r="L559" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
       <c r="M559" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
     </row>
     <row r="560">
@@ -25369,10 +25372,10 @@
         <v>22</v>
       </c>
       <c r="L560" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
       <c r="M560" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
     </row>
     <row r="561">
@@ -25410,10 +25413,10 @@
         <v>22</v>
       </c>
       <c r="L561" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
       <c r="M561" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
     </row>
     <row r="562">
@@ -25451,10 +25454,10 @@
         <v>22</v>
       </c>
       <c r="L562" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
       <c r="M562" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
     </row>
     <row r="563">
@@ -25492,10 +25495,10 @@
         <v>22</v>
       </c>
       <c r="L563" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
       <c r="M563" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
     </row>
     <row r="564">
@@ -25533,10 +25536,10 @@
         <v>22</v>
       </c>
       <c r="L564" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
       <c r="M564" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
     </row>
     <row r="565">
@@ -25574,10 +25577,10 @@
         <v>22</v>
       </c>
       <c r="L565" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
       <c r="M565" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
     </row>
     <row r="566">
@@ -25615,10 +25618,10 @@
         <v>22</v>
       </c>
       <c r="L566" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
       <c r="M566" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
     </row>
     <row r="567">
@@ -25656,10 +25659,10 @@
         <v>22</v>
       </c>
       <c r="L567" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
       <c r="M567" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
     </row>
     <row r="568">
@@ -25697,10 +25700,10 @@
         <v>22</v>
       </c>
       <c r="L568" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
       <c r="M568" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
     </row>
     <row r="569">
@@ -25738,10 +25741,10 @@
         <v>22</v>
       </c>
       <c r="L569" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
       <c r="M569" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
     </row>
     <row r="570">
@@ -25779,10 +25782,10 @@
         <v>22</v>
       </c>
       <c r="L570" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
       <c r="M570" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
     </row>
     <row r="571">
@@ -25820,10 +25823,10 @@
         <v>22</v>
       </c>
       <c r="L571" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
       <c r="M571" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
     </row>
     <row r="572">
@@ -25861,10 +25864,10 @@
         <v>22</v>
       </c>
       <c r="L572" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
       <c r="M572" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
     </row>
     <row r="573">
@@ -25902,10 +25905,10 @@
         <v>22</v>
       </c>
       <c r="L573" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
       <c r="M573" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
     </row>
     <row r="574">
@@ -25943,10 +25946,10 @@
         <v>22</v>
       </c>
       <c r="L574" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
       <c r="M574" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
     </row>
     <row r="575">
@@ -25984,10 +25987,10 @@
         <v>22</v>
       </c>
       <c r="L575" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
       <c r="M575" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
     </row>
     <row r="576">
@@ -26025,10 +26028,10 @@
         <v>22</v>
       </c>
       <c r="L576" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
       <c r="M576" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
     </row>
     <row r="577">
@@ -26066,10 +26069,10 @@
         <v>22</v>
       </c>
       <c r="L577" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
       <c r="M577" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
     </row>
     <row r="578">
@@ -26107,10 +26110,10 @@
         <v>22</v>
       </c>
       <c r="L578" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
       <c r="M578" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
     </row>
     <row r="579">
@@ -26148,10 +26151,10 @@
         <v>22</v>
       </c>
       <c r="L579" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
       <c r="M579" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
     </row>
     <row r="580">
@@ -26189,10 +26192,10 @@
         <v>22</v>
       </c>
       <c r="L580" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
       <c r="M580" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
     </row>
     <row r="581">
@@ -26230,10 +26233,10 @@
         <v>22</v>
       </c>
       <c r="L581" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
       <c r="M581" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
     </row>
     <row r="582">
@@ -26271,10 +26274,10 @@
         <v>22</v>
       </c>
       <c r="L582" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
       <c r="M582" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
     </row>
     <row r="583">
@@ -26312,10 +26315,10 @@
         <v>22</v>
       </c>
       <c r="L583" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
       <c r="M583" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
     </row>
     <row r="584">
@@ -26353,10 +26356,10 @@
         <v>22</v>
       </c>
       <c r="L584" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
       <c r="M584" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
     </row>
     <row r="585">
@@ -26394,10 +26397,10 @@
         <v>22</v>
       </c>
       <c r="L585" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
       <c r="M585" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
     </row>
     <row r="586">
@@ -26435,10 +26438,10 @@
         <v>22</v>
       </c>
       <c r="L586" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
       <c r="M586" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
     </row>
     <row r="587">
@@ -26476,10 +26479,10 @@
         <v>22</v>
       </c>
       <c r="L587" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
       <c r="M587" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
     </row>
     <row r="588">
@@ -26517,10 +26520,10 @@
         <v>22</v>
       </c>
       <c r="L588" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
       <c r="M588" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
     </row>
     <row r="589">
@@ -26558,10 +26561,10 @@
         <v>22</v>
       </c>
       <c r="L589" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
       <c r="M589" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
     </row>
     <row r="590">
@@ -26599,10 +26602,10 @@
         <v>22</v>
       </c>
       <c r="L590" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
       <c r="M590" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
     </row>
     <row r="591">
@@ -26640,10 +26643,10 @@
         <v>22</v>
       </c>
       <c r="L591" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
       <c r="M591" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
     </row>
     <row r="592">
@@ -26681,10 +26684,10 @@
         <v>22</v>
       </c>
       <c r="L592" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
       <c r="M592" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
     </row>
     <row r="593">
@@ -26722,10 +26725,10 @@
         <v>22</v>
       </c>
       <c r="L593" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
       <c r="M593" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
     </row>
     <row r="594">
@@ -26763,10 +26766,10 @@
         <v>22</v>
       </c>
       <c r="L594" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
       <c r="M594" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
     </row>
     <row r="595">
@@ -26804,10 +26807,10 @@
         <v>22</v>
       </c>
       <c r="L595" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
       <c r="M595" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
     </row>
     <row r="596">
@@ -26845,10 +26848,10 @@
         <v>22</v>
       </c>
       <c r="L596" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
       <c r="M596" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
     </row>
     <row r="597">
@@ -26886,10 +26889,10 @@
         <v>22</v>
       </c>
       <c r="L597" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
       <c r="M597" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
     </row>
     <row r="598">
@@ -26927,10 +26930,10 @@
         <v>22</v>
       </c>
       <c r="L598" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
       <c r="M598" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
     </row>
     <row r="599">
@@ -26968,10 +26971,10 @@
         <v>22</v>
       </c>
       <c r="L599" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
       <c r="M599" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
     </row>
     <row r="600">
@@ -27009,10 +27012,10 @@
         <v>22</v>
       </c>
       <c r="L600" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
       <c r="M600" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
     </row>
     <row r="601">
@@ -27050,10 +27053,10 @@
         <v>22</v>
       </c>
       <c r="L601" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
       <c r="M601" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
     </row>
     <row r="602">
@@ -27091,10 +27094,10 @@
         <v>22</v>
       </c>
       <c r="L602" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
       <c r="M602" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
     </row>
     <row r="603">
@@ -27132,10 +27135,10 @@
         <v>22</v>
       </c>
       <c r="L603" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
       <c r="M603" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
     </row>
     <row r="604">
@@ -27173,10 +27176,10 @@
         <v>22</v>
       </c>
       <c r="L604" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
       <c r="M604" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
     </row>
     <row r="605">
@@ -27214,10 +27217,10 @@
         <v>22</v>
       </c>
       <c r="L605" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
       <c r="M605" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
     </row>
     <row r="606">
@@ -27255,10 +27258,10 @@
         <v>22</v>
       </c>
       <c r="L606" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
       <c r="M606" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
     </row>
     <row r="607">
@@ -27296,10 +27299,10 @@
         <v>22</v>
       </c>
       <c r="L607" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
       <c r="M607" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
     </row>
     <row r="608">
@@ -27337,10 +27340,10 @@
         <v>22</v>
       </c>
       <c r="L608" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
       <c r="M608" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
     </row>
     <row r="609">
@@ -27378,10 +27381,10 @@
         <v>22</v>
       </c>
       <c r="L609" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
       <c r="M609" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
     </row>
     <row r="610">
@@ -27419,10 +27422,10 @@
         <v>22</v>
       </c>
       <c r="L610" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
       <c r="M610" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
     </row>
     <row r="611">
@@ -27460,10 +27463,10 @@
         <v>22</v>
       </c>
       <c r="L611" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
       <c r="M611" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
     </row>
     <row r="612">
@@ -27501,10 +27504,10 @@
         <v>22</v>
       </c>
       <c r="L612" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
       <c r="M612" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
     </row>
     <row r="613">
@@ -27542,10 +27545,10 @@
         <v>22</v>
       </c>
       <c r="L613" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
       <c r="M613" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
     </row>
     <row r="614">
@@ -27583,10 +27586,10 @@
         <v>22</v>
       </c>
       <c r="L614" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
       <c r="M614" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
     </row>
     <row r="615">
@@ -27624,10 +27627,10 @@
         <v>22</v>
       </c>
       <c r="L615" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
       <c r="M615" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
     </row>
     <row r="616">
@@ -27665,10 +27668,10 @@
         <v>22</v>
       </c>
       <c r="L616" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
       <c r="M616" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
     </row>
     <row r="617">
@@ -27706,10 +27709,10 @@
         <v>22</v>
       </c>
       <c r="L617" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
       <c r="M617" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
     </row>
     <row r="618">
@@ -27747,10 +27750,10 @@
         <v>22</v>
       </c>
       <c r="L618" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
       <c r="M618" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
     </row>
     <row r="619">
@@ -27788,10 +27791,10 @@
         <v>22</v>
       </c>
       <c r="L619" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
       <c r="M619" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
     </row>
     <row r="620">
@@ -27829,10 +27832,10 @@
         <v>22</v>
       </c>
       <c r="L620" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
       <c r="M620" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
     </row>
     <row r="621">
@@ -27870,10 +27873,10 @@
         <v>22</v>
       </c>
       <c r="L621" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
       <c r="M621" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
     </row>
     <row r="622">
@@ -27911,10 +27914,10 @@
         <v>22</v>
       </c>
       <c r="L622" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
       <c r="M622" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
     </row>
     <row r="623">
@@ -27952,10 +27955,10 @@
         <v>22</v>
       </c>
       <c r="L623" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
       <c r="M623" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
     </row>
     <row r="624">
@@ -27993,10 +27996,10 @@
         <v>22</v>
       </c>
       <c r="L624" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
       <c r="M624" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
     </row>
     <row r="625">
@@ -28034,10 +28037,10 @@
         <v>22</v>
       </c>
       <c r="L625" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
       <c r="M625" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
     </row>
     <row r="626">
@@ -28075,10 +28078,10 @@
         <v>22</v>
       </c>
       <c r="L626" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
       <c r="M626" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
     </row>
     <row r="627">
@@ -28116,10 +28119,10 @@
         <v>22</v>
       </c>
       <c r="L627" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
       <c r="M627" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
     </row>
     <row r="628">
@@ -28157,10 +28160,10 @@
         <v>22</v>
       </c>
       <c r="L628" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
       <c r="M628" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
     </row>
     <row r="629">
@@ -28198,10 +28201,10 @@
         <v>22</v>
       </c>
       <c r="L629" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
       <c r="M629" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
     </row>
     <row r="630">
@@ -28239,10 +28242,10 @@
         <v>22</v>
       </c>
       <c r="L630" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
       <c r="M630" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
     </row>
     <row r="631">
@@ -28280,10 +28283,10 @@
         <v>22</v>
       </c>
       <c r="L631" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
       <c r="M631" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
     </row>
     <row r="632">
@@ -28321,10 +28324,10 @@
         <v>22</v>
       </c>
       <c r="L632" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
       <c r="M632" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
     </row>
     <row r="633">
@@ -28362,10 +28365,10 @@
         <v>22</v>
       </c>
       <c r="L633" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
       <c r="M633" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
     </row>
     <row r="634">
@@ -28403,10 +28406,10 @@
         <v>22</v>
       </c>
       <c r="L634" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
       <c r="M634" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
     </row>
     <row r="635">
@@ -28444,10 +28447,10 @@
         <v>22</v>
       </c>
       <c r="L635" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
       <c r="M635" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
     </row>
     <row r="636">
@@ -28485,10 +28488,10 @@
         <v>22</v>
       </c>
       <c r="L636" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
       <c r="M636" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
     </row>
     <row r="637">
@@ -28526,10 +28529,10 @@
         <v>22</v>
       </c>
       <c r="L637" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
       <c r="M637" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
     </row>
     <row r="638">
@@ -28567,10 +28570,10 @@
         <v>22</v>
       </c>
       <c r="L638" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
       <c r="M638" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
     </row>
     <row r="639">
@@ -28608,10 +28611,10 @@
         <v>22</v>
       </c>
       <c r="L639" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
       <c r="M639" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
     </row>
     <row r="640">
@@ -28649,10 +28652,10 @@
         <v>22</v>
       </c>
       <c r="L640" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
       <c r="M640" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
     </row>
     <row r="641">
@@ -28690,10 +28693,10 @@
         <v>22</v>
       </c>
       <c r="L641" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
       <c r="M641" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
     </row>
     <row r="642">
@@ -28731,10 +28734,10 @@
         <v>22</v>
       </c>
       <c r="L642" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
       <c r="M642" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
     </row>
     <row r="643">
@@ -28772,10 +28775,10 @@
         <v>22</v>
       </c>
       <c r="L643" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
       <c r="M643" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
     </row>
     <row r="644">
@@ -28813,10 +28816,10 @@
         <v>22</v>
       </c>
       <c r="L644" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
       <c r="M644" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
     </row>
     <row r="645">
@@ -28854,10 +28857,10 @@
         <v>22</v>
       </c>
       <c r="L645" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
       <c r="M645" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
     </row>
     <row r="646">
@@ -28895,10 +28898,10 @@
         <v>22</v>
       </c>
       <c r="L646" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
       <c r="M646" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
     </row>
     <row r="647">
@@ -28936,10 +28939,10 @@
         <v>22</v>
       </c>
       <c r="L647" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
       <c r="M647" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
     </row>
     <row r="648">
@@ -28977,10 +28980,10 @@
         <v>22</v>
       </c>
       <c r="L648" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
       <c r="M648" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
     </row>
     <row r="649">
@@ -29018,10 +29021,10 @@
         <v>22</v>
       </c>
       <c r="L649" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
       <c r="M649" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
     </row>
     <row r="650">
@@ -29059,10 +29062,10 @@
         <v>22</v>
       </c>
       <c r="L650" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
       <c r="M650" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
     </row>
     <row r="651">
@@ -29100,10 +29103,10 @@
         <v>22</v>
       </c>
       <c r="L651" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
       <c r="M651" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
     </row>
     <row r="652">
@@ -29141,10 +29144,10 @@
         <v>22</v>
       </c>
       <c r="L652" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
       <c r="M652" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
     </row>
     <row r="653">
@@ -29182,10 +29185,10 @@
         <v>22</v>
       </c>
       <c r="L653" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
       <c r="M653" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
     </row>
     <row r="654">
@@ -29223,10 +29226,10 @@
         <v>22</v>
       </c>
       <c r="L654" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
       <c r="M654" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
     </row>
     <row r="655">
@@ -29264,10 +29267,10 @@
         <v>22</v>
       </c>
       <c r="L655" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
       <c r="M655" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
     </row>
     <row r="656">
@@ -29305,10 +29308,10 @@
         <v>22</v>
       </c>
       <c r="L656" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
       <c r="M656" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
     </row>
     <row r="657">
@@ -29346,10 +29349,10 @@
         <v>22</v>
       </c>
       <c r="L657" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
       <c r="M657" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
     </row>
     <row r="658">
@@ -29387,10 +29390,10 @@
         <v>22</v>
       </c>
       <c r="L658" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
       <c r="M658" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
     </row>
     <row r="659">
@@ -29428,10 +29431,10 @@
         <v>22</v>
       </c>
       <c r="L659" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
       <c r="M659" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
     </row>
     <row r="660">
@@ -29469,10 +29472,10 @@
         <v>22</v>
       </c>
       <c r="L660" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
       <c r="M660" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
     </row>
     <row r="661">
@@ -29510,10 +29513,10 @@
         <v>22</v>
       </c>
       <c r="L661" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
       <c r="M661" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
     </row>
     <row r="662">
@@ -29551,10 +29554,10 @@
         <v>22</v>
       </c>
       <c r="L662" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
       <c r="M662" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
     </row>
     <row r="663">
@@ -29592,10 +29595,10 @@
         <v>22</v>
       </c>
       <c r="L663" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
       <c r="M663" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
     </row>
     <row r="664">
@@ -29633,10 +29636,10 @@
         <v>22</v>
       </c>
       <c r="L664" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
       <c r="M664" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
     </row>
     <row r="665">
@@ -29674,10 +29677,10 @@
         <v>22</v>
       </c>
       <c r="L665" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
       <c r="M665" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
     </row>
     <row r="666">
@@ -29715,10 +29718,10 @@
         <v>22</v>
       </c>
       <c r="L666" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
       <c r="M666" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
     </row>
     <row r="667">
@@ -29756,10 +29759,10 @@
         <v>22</v>
       </c>
       <c r="L667" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
       <c r="M667" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
     </row>
     <row r="668">
@@ -29797,10 +29800,10 @@
         <v>22</v>
       </c>
       <c r="L668" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
       <c r="M668" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
     </row>
     <row r="669">
@@ -29838,10 +29841,10 @@
         <v>22</v>
       </c>
       <c r="L669" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
       <c r="M669" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
     </row>
     <row r="670">
@@ -29879,10 +29882,10 @@
         <v>22</v>
       </c>
       <c r="L670" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
       <c r="M670" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
     </row>
     <row r="671">
@@ -29920,10 +29923,10 @@
         <v>22</v>
       </c>
       <c r="L671" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
       <c r="M671" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
     </row>
     <row r="672">
@@ -29961,10 +29964,10 @@
         <v>22</v>
       </c>
       <c r="L672" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
       <c r="M672" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
     </row>
     <row r="673">
@@ -30002,10 +30005,10 @@
         <v>22</v>
       </c>
       <c r="L673" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
       <c r="M673" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
     </row>
     <row r="674">
@@ -30043,10 +30046,10 @@
         <v>22</v>
       </c>
       <c r="L674" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
       <c r="M674" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
     </row>
     <row r="675">
@@ -30084,10 +30087,10 @@
         <v>22</v>
       </c>
       <c r="L675" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
       <c r="M675" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
     </row>
     <row r="676">
@@ -30125,10 +30128,10 @@
         <v>22</v>
       </c>
       <c r="L676" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
       <c r="M676" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
     </row>
     <row r="677">
@@ -30166,10 +30169,10 @@
         <v>22</v>
       </c>
       <c r="L677" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
       <c r="M677" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
     </row>
     <row r="678">
@@ -30207,10 +30210,10 @@
         <v>22</v>
       </c>
       <c r="L678" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
       <c r="M678" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
     </row>
     <row r="679">
@@ -30248,10 +30251,10 @@
         <v>22</v>
       </c>
       <c r="L679" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
       <c r="M679" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
     </row>
     <row r="680">
@@ -30289,10 +30292,10 @@
         <v>22</v>
       </c>
       <c r="L680" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
       <c r="M680" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
     </row>
     <row r="681">
@@ -30330,10 +30333,10 @@
         <v>22</v>
       </c>
       <c r="L681" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
       <c r="M681" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
     </row>
     <row r="682">
@@ -30371,10 +30374,10 @@
         <v>22</v>
       </c>
       <c r="L682" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
       <c r="M682" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
     </row>
     <row r="683">
@@ -30412,10 +30415,10 @@
         <v>22</v>
       </c>
       <c r="L683" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
       <c r="M683" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
     </row>
     <row r="684">
@@ -30453,10 +30456,10 @@
         <v>22</v>
       </c>
       <c r="L684" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
       <c r="M684" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
     </row>
     <row r="685">
@@ -30494,10 +30497,10 @@
         <v>22</v>
       </c>
       <c r="L685" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
       <c r="M685" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
     </row>
     <row r="686">
@@ -30535,10 +30538,10 @@
         <v>22</v>
       </c>
       <c r="L686" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
       <c r="M686" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
     </row>
     <row r="687">
@@ -30576,10 +30579,10 @@
         <v>22</v>
       </c>
       <c r="L687" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
       <c r="M687" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
     </row>
     <row r="688">
@@ -30617,10 +30620,10 @@
         <v>22</v>
       </c>
       <c r="L688" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
       <c r="M688" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
     </row>
     <row r="689">
@@ -30658,10 +30661,10 @@
         <v>22</v>
       </c>
       <c r="L689" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
       <c r="M689" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
     </row>
     <row r="690">
@@ -30699,10 +30702,10 @@
         <v>22</v>
       </c>
       <c r="L690" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
       <c r="M690" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
     </row>
     <row r="691">
@@ -30740,10 +30743,10 @@
         <v>22</v>
       </c>
       <c r="L691" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
       <c r="M691" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
     </row>
     <row r="692">
@@ -30781,10 +30784,10 @@
         <v>22</v>
       </c>
       <c r="L692" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
       <c r="M692" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
     </row>
     <row r="693">
@@ -30822,10 +30825,10 @@
         <v>22</v>
       </c>
       <c r="L693" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
       <c r="M693" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
     </row>
     <row r="694">
@@ -30863,10 +30866,10 @@
         <v>22</v>
       </c>
       <c r="L694" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
       <c r="M694" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
     </row>
     <row r="695">
@@ -30904,10 +30907,10 @@
         <v>22</v>
       </c>
       <c r="L695" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
       <c r="M695" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
     </row>
     <row r="696">
@@ -30945,10 +30948,10 @@
         <v>22</v>
       </c>
       <c r="L696" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
       <c r="M696" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
     </row>
     <row r="697">
@@ -30986,10 +30989,10 @@
         <v>22</v>
       </c>
       <c r="L697" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
       <c r="M697" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
     </row>
     <row r="698">
@@ -31027,10 +31030,10 @@
         <v>22</v>
       </c>
       <c r="L698" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
       <c r="M698" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
     </row>
     <row r="699">
@@ -31068,10 +31071,10 @@
         <v>22</v>
       </c>
       <c r="L699" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
       <c r="M699" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
     </row>
     <row r="700">
@@ -31109,10 +31112,10 @@
         <v>22</v>
       </c>
       <c r="L700" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
       <c r="M700" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
     </row>
     <row r="701">
@@ -31150,10 +31153,10 @@
         <v>22</v>
       </c>
       <c r="L701" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
       <c r="M701" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
     </row>
     <row r="702">
@@ -31191,10 +31194,10 @@
         <v>22</v>
       </c>
       <c r="L702" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
       <c r="M702" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
     </row>
     <row r="703">
@@ -31232,10 +31235,10 @@
         <v>22</v>
       </c>
       <c r="L703" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
       <c r="M703" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
     </row>
     <row r="704">
@@ -31273,10 +31276,10 @@
         <v>22</v>
       </c>
       <c r="L704" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
       <c r="M704" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
     </row>
     <row r="705">
@@ -31314,10 +31317,10 @@
         <v>22</v>
       </c>
       <c r="L705" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
       <c r="M705" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
     </row>
     <row r="706">
@@ -31355,10 +31358,10 @@
         <v>22</v>
       </c>
       <c r="L706" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
       <c r="M706" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
     </row>
     <row r="707">
@@ -31396,10 +31399,10 @@
         <v>22</v>
       </c>
       <c r="L707" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
       <c r="M707" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
     </row>
     <row r="708">
@@ -31437,10 +31440,10 @@
         <v>22</v>
       </c>
       <c r="L708" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
       <c r="M708" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
     </row>
     <row r="709">
@@ -31478,10 +31481,10 @@
         <v>22</v>
       </c>
       <c r="L709" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
       <c r="M709" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
     </row>
     <row r="710">
@@ -31519,10 +31522,10 @@
         <v>22</v>
       </c>
       <c r="L710" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
       <c r="M710" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
     </row>
     <row r="711">
@@ -31560,10 +31563,10 @@
         <v>22</v>
       </c>
       <c r="L711" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
       <c r="M711" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
     </row>
     <row r="712">
@@ -31601,10 +31604,10 @@
         <v>22</v>
       </c>
       <c r="L712" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
       <c r="M712" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
     </row>
     <row r="713">
@@ -31642,10 +31645,10 @@
         <v>22</v>
       </c>
       <c r="L713" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
       <c r="M713" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
     </row>
     <row r="714">
@@ -31683,10 +31686,10 @@
         <v>22</v>
       </c>
       <c r="L714" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
       <c r="M714" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
     </row>
     <row r="715">
@@ -31724,10 +31727,10 @@
         <v>22</v>
       </c>
       <c r="L715" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
       <c r="M715" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
     </row>
     <row r="716">
@@ -31765,10 +31768,10 @@
         <v>22</v>
       </c>
       <c r="L716" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
       <c r="M716" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
     </row>
     <row r="717">
@@ -31806,10 +31809,10 @@
         <v>22</v>
       </c>
       <c r="L717" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
       <c r="M717" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
     </row>
     <row r="718">
@@ -31847,10 +31850,10 @@
         <v>22</v>
       </c>
       <c r="L718" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
       <c r="M718" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
     </row>
     <row r="719">
@@ -31888,10 +31891,10 @@
         <v>22</v>
       </c>
       <c r="L719" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
       <c r="M719" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
     </row>
     <row r="720">
@@ -31929,10 +31932,10 @@
         <v>22</v>
       </c>
       <c r="L720" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
       <c r="M720" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
     </row>
     <row r="721">
@@ -31970,10 +31973,10 @@
         <v>22</v>
       </c>
       <c r="L721" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
       <c r="M721" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
     </row>
     <row r="722">
@@ -32011,10 +32014,10 @@
         <v>22</v>
       </c>
       <c r="L722" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
       <c r="M722" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
     </row>
     <row r="723">
@@ -32052,10 +32055,10 @@
         <v>22</v>
       </c>
       <c r="L723" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
       <c r="M723" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
     </row>
     <row r="724">
@@ -32093,10 +32096,10 @@
         <v>22</v>
       </c>
       <c r="L724" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
       <c r="M724" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
     </row>
     <row r="725">
@@ -32134,10 +32137,10 @@
         <v>22</v>
       </c>
       <c r="L725" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
       <c r="M725" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
     </row>
     <row r="726">
@@ -32175,10 +32178,10 @@
         <v>22</v>
       </c>
       <c r="L726" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
       <c r="M726" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
     </row>
     <row r="727">
@@ -32216,10 +32219,10 @@
         <v>22</v>
       </c>
       <c r="L727" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
       <c r="M727" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
     </row>
     <row r="728">
@@ -32257,10 +32260,10 @@
         <v>22</v>
       </c>
       <c r="L728" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
       <c r="M728" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
     </row>
     <row r="729">
@@ -32298,10 +32301,10 @@
         <v>22</v>
       </c>
       <c r="L729" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
       <c r="M729" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
     </row>
     <row r="730">
@@ -32339,10 +32342,10 @@
         <v>22</v>
       </c>
       <c r="L730" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
       <c r="M730" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
     </row>
     <row r="731">
@@ -32380,10 +32383,10 @@
         <v>22</v>
       </c>
       <c r="L731" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
       <c r="M731" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
     </row>
     <row r="732">
@@ -32421,10 +32424,10 @@
         <v>22</v>
       </c>
       <c r="L732" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
       <c r="M732" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
     </row>
     <row r="733">
@@ -32462,10 +32465,10 @@
         <v>22</v>
       </c>
       <c r="L733" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
       <c r="M733" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
     </row>
     <row r="734">
@@ -32503,10 +32506,10 @@
         <v>22</v>
       </c>
       <c r="L734" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
       <c r="M734" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
     </row>
     <row r="735">
@@ -32544,10 +32547,10 @@
         <v>22</v>
       </c>
       <c r="L735" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
       <c r="M735" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
     </row>
     <row r="736">
@@ -32585,10 +32588,10 @@
         <v>22</v>
       </c>
       <c r="L736" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
       <c r="M736" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
     </row>
     <row r="737">
@@ -32626,10 +32629,10 @@
         <v>22</v>
       </c>
       <c r="L737" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
       <c r="M737" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
     </row>
     <row r="738">
@@ -32667,10 +32670,10 @@
         <v>22</v>
       </c>
       <c r="L738" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
       <c r="M738" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
     </row>
     <row r="739">
@@ -32708,10 +32711,10 @@
         <v>22</v>
       </c>
       <c r="L739" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
       <c r="M739" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
     </row>
     <row r="740">
@@ -32749,10 +32752,10 @@
         <v>22</v>
       </c>
       <c r="L740" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
       <c r="M740" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
     </row>
     <row r="741">
@@ -32790,10 +32793,10 @@
         <v>22</v>
       </c>
       <c r="L741" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
       <c r="M741" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
     </row>
     <row r="742">
@@ -32831,10 +32834,10 @@
         <v>22</v>
       </c>
       <c r="L742" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
       <c r="M742" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
     </row>
     <row r="743">
@@ -32872,10 +32875,10 @@
         <v>22</v>
       </c>
       <c r="L743" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
       <c r="M743" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
     </row>
     <row r="744">
@@ -32913,10 +32916,10 @@
         <v>22</v>
       </c>
       <c r="L744" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
       <c r="M744" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
     </row>
     <row r="745">
@@ -32954,10 +32957,10 @@
         <v>22</v>
       </c>
       <c r="L745" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
       <c r="M745" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
     </row>
     <row r="746">
@@ -32995,10 +32998,10 @@
         <v>22</v>
       </c>
       <c r="L746" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
       <c r="M746" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
     </row>
     <row r="747">
@@ -33036,10 +33039,10 @@
         <v>22</v>
       </c>
       <c r="L747" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
       <c r="M747" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
     </row>
     <row r="748">
@@ -33077,10 +33080,10 @@
         <v>22</v>
       </c>
       <c r="L748" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
       <c r="M748" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
     </row>
     <row r="749">
@@ -33118,10 +33121,10 @@
         <v>22</v>
       </c>
       <c r="L749" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
       <c r="M749" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
     </row>
     <row r="750">
@@ -33159,10 +33162,10 @@
         <v>22</v>
       </c>
       <c r="L750" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
       <c r="M750" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
     </row>
     <row r="751">
@@ -33200,10 +33203,10 @@
         <v>22</v>
       </c>
       <c r="L751" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
       <c r="M751" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
     </row>
     <row r="752">
@@ -33241,10 +33244,10 @@
         <v>22</v>
       </c>
       <c r="L752" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
       <c r="M752" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
     </row>
     <row r="753">
@@ -33282,10 +33285,10 @@
         <v>22</v>
       </c>
       <c r="L753" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
       <c r="M753" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
     </row>
     <row r="754">
@@ -33323,10 +33326,10 @@
         <v>22</v>
       </c>
       <c r="L754" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
       <c r="M754" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
     </row>
     <row r="755">
@@ -33364,10 +33367,10 @@
         <v>22</v>
       </c>
       <c r="L755" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
       <c r="M755" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
     </row>
     <row r="756">
@@ -33405,10 +33408,10 @@
         <v>22</v>
       </c>
       <c r="L756" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
       <c r="M756" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
     </row>
     <row r="757">
@@ -33446,10 +33449,10 @@
         <v>22</v>
       </c>
       <c r="L757" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
       <c r="M757" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
     </row>
     <row r="758">
@@ -33487,10 +33490,10 @@
         <v>22</v>
       </c>
       <c r="L758" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
       <c r="M758" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
     </row>
     <row r="759">
@@ -33528,10 +33531,10 @@
         <v>22</v>
       </c>
       <c r="L759" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
       <c r="M759" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
     </row>
     <row r="760">
@@ -33569,10 +33572,10 @@
         <v>22</v>
       </c>
       <c r="L760" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
       <c r="M760" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
     </row>
     <row r="761">
@@ -33610,10 +33613,10 @@
         <v>22</v>
       </c>
       <c r="L761" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
       <c r="M761" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
     </row>
     <row r="762">
@@ -33651,10 +33654,10 @@
         <v>22</v>
       </c>
       <c r="L762" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
       <c r="M762" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
     </row>
     <row r="763">
@@ -33692,10 +33695,10 @@
         <v>22</v>
       </c>
       <c r="L763" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
       <c r="M763" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
     </row>
     <row r="764">
@@ -33733,10 +33736,10 @@
         <v>22</v>
       </c>
       <c r="L764" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
       <c r="M764" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
     </row>
     <row r="765">
@@ -33774,10 +33777,10 @@
         <v>22</v>
       </c>
       <c r="L765" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
       <c r="M765" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
     </row>
     <row r="766">
@@ -33815,10 +33818,10 @@
         <v>22</v>
       </c>
       <c r="L766" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
       <c r="M766" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
     </row>
     <row r="767">
@@ -33856,10 +33859,10 @@
         <v>22</v>
       </c>
       <c r="L767" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
       <c r="M767" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
     </row>
     <row r="768">
@@ -33897,10 +33900,10 @@
         <v>22</v>
       </c>
       <c r="L768" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
       <c r="M768" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
     </row>
     <row r="769">
@@ -33938,10 +33941,10 @@
         <v>22</v>
       </c>
       <c r="L769" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
       <c r="M769" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
     </row>
     <row r="770">
@@ -33979,10 +33982,10 @@
         <v>22</v>
       </c>
       <c r="L770" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
       <c r="M770" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
     </row>
     <row r="771">
@@ -34020,10 +34023,10 @@
         <v>22</v>
       </c>
       <c r="L771" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
       <c r="M771" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
     </row>
     <row r="772">
@@ -34061,10 +34064,10 @@
         <v>22</v>
       </c>
       <c r="L772" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
       <c r="M772" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
     </row>
     <row r="773">
@@ -34102,10 +34105,10 @@
         <v>22</v>
       </c>
       <c r="L773" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
       <c r="M773" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
     </row>
     <row r="774">
@@ -34143,10 +34146,10 @@
         <v>22</v>
       </c>
       <c r="L774" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
       <c r="M774" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
     </row>
     <row r="775">
@@ -34184,10 +34187,10 @@
         <v>22</v>
       </c>
       <c r="L775" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
       <c r="M775" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
     </row>
     <row r="776">
@@ -34225,10 +34228,10 @@
         <v>22</v>
       </c>
       <c r="L776" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
       <c r="M776" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
     </row>
     <row r="777">
@@ -34266,10 +34269,10 @@
         <v>22</v>
       </c>
       <c r="L777" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
       <c r="M777" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
     </row>
     <row r="778">
@@ -34307,10 +34310,10 @@
         <v>22</v>
       </c>
       <c r="L778" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
       <c r="M778" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
     </row>
     <row r="779">
@@ -34348,10 +34351,10 @@
         <v>22</v>
       </c>
       <c r="L779" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
       <c r="M779" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
     </row>
     <row r="780">
@@ -34389,10 +34392,10 @@
         <v>22</v>
       </c>
       <c r="L780" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
       <c r="M780" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
     </row>
     <row r="781">
@@ -34430,10 +34433,10 @@
         <v>22</v>
       </c>
       <c r="L781" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
       <c r="M781" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
     </row>
     <row r="782">
@@ -34471,10 +34474,10 @@
         <v>22</v>
       </c>
       <c r="L782" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
       <c r="M782" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
     </row>
     <row r="783">
@@ -34512,10 +34515,10 @@
         <v>22</v>
       </c>
       <c r="L783" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
       <c r="M783" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
     </row>
     <row r="784">
@@ -34553,10 +34556,10 @@
         <v>22</v>
       </c>
       <c r="L784" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
       <c r="M784" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
     </row>
     <row r="785">
@@ -34594,10 +34597,10 @@
         <v>22</v>
       </c>
       <c r="L785" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
       <c r="M785" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
     </row>
     <row r="786">
@@ -34635,10 +34638,10 @@
         <v>22</v>
       </c>
       <c r="L786" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
       <c r="M786" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
     </row>
     <row r="787">
@@ -34676,10 +34679,10 @@
         <v>22</v>
       </c>
       <c r="L787" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
       <c r="M787" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
     </row>
     <row r="788">
@@ -34717,10 +34720,10 @@
         <v>22</v>
       </c>
       <c r="L788" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
       <c r="M788" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
     </row>
     <row r="789">
@@ -34758,10 +34761,10 @@
         <v>22</v>
       </c>
       <c r="L789" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
       <c r="M789" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
     </row>
     <row r="790">
@@ -34799,10 +34802,10 @@
         <v>22</v>
       </c>
       <c r="L790" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
       <c r="M790" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
     </row>
     <row r="791">
@@ -34840,10 +34843,10 @@
         <v>22</v>
       </c>
       <c r="L791" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
       <c r="M791" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
     </row>
     <row r="792">
@@ -34881,10 +34884,10 @@
         <v>22</v>
       </c>
       <c r="L792" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
       <c r="M792" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
     </row>
     <row r="793">
@@ -34922,10 +34925,10 @@
         <v>22</v>
       </c>
       <c r="L793" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
       <c r="M793" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
     </row>
     <row r="794">
@@ -34963,10 +34966,10 @@
         <v>22</v>
       </c>
       <c r="L794" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
       <c r="M794" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
     </row>
     <row r="795">
@@ -35004,10 +35007,10 @@
         <v>22</v>
       </c>
       <c r="L795" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
       <c r="M795" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
     </row>
     <row r="796">
@@ -35045,10 +35048,10 @@
         <v>22</v>
       </c>
       <c r="L796" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
       <c r="M796" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
     </row>
     <row r="797">
@@ -35086,10 +35089,10 @@
         <v>22</v>
       </c>
       <c r="L797" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
       <c r="M797" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
     </row>
     <row r="798">
@@ -35127,10 +35130,10 @@
         <v>22</v>
       </c>
       <c r="L798" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
       <c r="M798" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
     </row>
     <row r="799">
@@ -35168,10 +35171,10 @@
         <v>22</v>
       </c>
       <c r="L799" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
       <c r="M799" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
     </row>
     <row r="800">
@@ -35209,10 +35212,10 @@
         <v>22</v>
       </c>
       <c r="L800" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
       <c r="M800" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
     </row>
     <row r="801">
@@ -35250,10 +35253,10 @@
         <v>22</v>
       </c>
       <c r="L801" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
       <c r="M801" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
     </row>
     <row r="802">
@@ -35291,10 +35294,10 @@
         <v>22</v>
       </c>
       <c r="L802" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
       <c r="M802" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
     </row>
     <row r="803">
@@ -35332,10 +35335,10 @@
         <v>22</v>
       </c>
       <c r="L803" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
       <c r="M803" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
     </row>
     <row r="804">
@@ -35373,10 +35376,10 @@
         <v>22</v>
       </c>
       <c r="L804" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
       <c r="M804" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
     </row>
     <row r="805">
@@ -35414,10 +35417,10 @@
         <v>22</v>
       </c>
       <c r="L805" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
       <c r="M805" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
     </row>
     <row r="806">
@@ -35455,10 +35458,10 @@
         <v>22</v>
       </c>
       <c r="L806" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
       <c r="M806" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
     </row>
     <row r="807">
@@ -35496,10 +35499,10 @@
         <v>22</v>
       </c>
       <c r="L807" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
       <c r="M807" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
     </row>
     <row r="808">
@@ -35537,10 +35540,10 @@
         <v>22</v>
       </c>
       <c r="L808" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
       <c r="M808" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
     </row>
     <row r="809">
@@ -35578,10 +35581,10 @@
         <v>22</v>
       </c>
       <c r="L809" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
       <c r="M809" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
     </row>
     <row r="810">
@@ -35619,10 +35622,10 @@
         <v>22</v>
       </c>
       <c r="L810" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
       <c r="M810" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
     </row>
     <row r="811">
@@ -35660,10 +35663,10 @@
         <v>22</v>
       </c>
       <c r="L811" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
       <c r="M811" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
     </row>
     <row r="812">
@@ -35701,10 +35704,10 @@
         <v>22</v>
       </c>
       <c r="L812" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
       <c r="M812" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
     </row>
     <row r="813">
@@ -35742,10 +35745,10 @@
         <v>22</v>
       </c>
       <c r="L813" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
       <c r="M813" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
     </row>
     <row r="814">
@@ -35783,10 +35786,10 @@
         <v>22</v>
       </c>
       <c r="L814" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
       <c r="M814" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
     </row>
     <row r="815">
@@ -35824,10 +35827,10 @@
         <v>22</v>
       </c>
       <c r="L815" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
       <c r="M815" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
     </row>
     <row r="816">
@@ -35865,10 +35868,10 @@
         <v>22</v>
       </c>
       <c r="L816" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
       <c r="M816" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
     </row>
     <row r="817">
@@ -35906,10 +35909,10 @@
         <v>22</v>
       </c>
       <c r="L817" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
       <c r="M817" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
     </row>
     <row r="818">
@@ -35947,10 +35950,10 @@
         <v>22</v>
       </c>
       <c r="L818" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
       <c r="M818" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
     </row>
     <row r="819">
@@ -35988,10 +35991,10 @@
         <v>22</v>
       </c>
       <c r="L819" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
       <c r="M819" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
     </row>
     <row r="820">
@@ -36029,10 +36032,10 @@
         <v>22</v>
       </c>
       <c r="L820" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
       <c r="M820" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
     </row>
     <row r="821">
@@ -36070,10 +36073,10 @@
         <v>22</v>
       </c>
       <c r="L821" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
       <c r="M821" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
     </row>
     <row r="822">
@@ -36111,10 +36114,10 @@
         <v>22</v>
       </c>
       <c r="L822" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
       <c r="M822" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
     </row>
     <row r="823">
@@ -36152,10 +36155,10 @@
         <v>22</v>
       </c>
       <c r="L823" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
       <c r="M823" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
     </row>
     <row r="824">
@@ -36193,10 +36196,10 @@
         <v>22</v>
       </c>
       <c r="L824" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
       <c r="M824" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
     </row>
     <row r="825">
@@ -36234,10 +36237,10 @@
         <v>22</v>
       </c>
       <c r="L825" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
       <c r="M825" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
     </row>
     <row r="826">
@@ -36275,10 +36278,10 @@
         <v>22</v>
       </c>
       <c r="L826" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
       <c r="M826" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
     </row>
     <row r="827">
@@ -36316,10 +36319,10 @@
         <v>22</v>
       </c>
       <c r="L827" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
       <c r="M827" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
     </row>
     <row r="828">
@@ -36357,10 +36360,10 @@
         <v>22</v>
       </c>
       <c r="L828" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
       <c r="M828" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
     </row>
     <row r="829">
@@ -36398,10 +36401,10 @@
         <v>22</v>
       </c>
       <c r="L829" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
       <c r="M829" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
     </row>
     <row r="830">
@@ -36439,10 +36442,10 @@
         <v>22</v>
       </c>
       <c r="L830" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
       <c r="M830" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
     </row>
     <row r="831">
@@ -36480,10 +36483,10 @@
         <v>22</v>
       </c>
       <c r="L831" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
       <c r="M831" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
     </row>
     <row r="832">
@@ -36521,10 +36524,10 @@
         <v>22</v>
       </c>
       <c r="L832" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
       <c r="M832" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
     </row>
     <row r="833">
@@ -36562,10 +36565,10 @@
         <v>22</v>
       </c>
       <c r="L833" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
       <c r="M833" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
     </row>
     <row r="834">
@@ -36603,10 +36606,10 @@
         <v>22</v>
       </c>
       <c r="L834" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
       <c r="M834" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
     </row>
     <row r="835">
@@ -36644,10 +36647,10 @@
         <v>22</v>
       </c>
       <c r="L835" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
       <c r="M835" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
     </row>
     <row r="836">
@@ -36685,10 +36688,10 @@
         <v>22</v>
       </c>
       <c r="L836" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
       <c r="M836" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
     </row>
     <row r="837">
@@ -36726,10 +36729,10 @@
         <v>22</v>
       </c>
       <c r="L837" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
       <c r="M837" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
     </row>
     <row r="838">
@@ -36767,10 +36770,10 @@
         <v>22</v>
       </c>
       <c r="L838" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
       <c r="M838" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
     </row>
     <row r="839">
@@ -36808,10 +36811,10 @@
         <v>22</v>
       </c>
       <c r="L839" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
       <c r="M839" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
     </row>
     <row r="840">
@@ -36849,10 +36852,10 @@
         <v>22</v>
       </c>
       <c r="L840" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
       <c r="M840" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
     </row>
     <row r="841">
@@ -36890,10 +36893,10 @@
         <v>22</v>
       </c>
       <c r="L841" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
       <c r="M841" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
     </row>
     <row r="842">
@@ -36931,10 +36934,10 @@
         <v>22</v>
       </c>
       <c r="L842" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
       <c r="M842" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
     </row>
     <row r="843">
@@ -36972,10 +36975,10 @@
         <v>22</v>
       </c>
       <c r="L843" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
       <c r="M843" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
     </row>
     <row r="844">
@@ -37013,10 +37016,10 @@
         <v>22</v>
       </c>
       <c r="L844" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
       <c r="M844" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
     </row>
     <row r="845">
@@ -37054,10 +37057,10 @@
         <v>22</v>
       </c>
       <c r="L845" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
       <c r="M845" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
     </row>
     <row r="846">
@@ -37095,10 +37098,10 @@
         <v>22</v>
       </c>
       <c r="L846" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
       <c r="M846" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
     </row>
     <row r="847">
@@ -37136,10 +37139,10 @@
         <v>22</v>
       </c>
       <c r="L847" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
       <c r="M847" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
     </row>
     <row r="848">
@@ -37177,10 +37180,10 @@
         <v>22</v>
       </c>
       <c r="L848" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
       <c r="M848" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
     </row>
     <row r="849">
@@ -37218,10 +37221,10 @@
         <v>22</v>
       </c>
       <c r="L849" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
       <c r="M849" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
     </row>
     <row r="850">
@@ -37259,10 +37262,10 @@
         <v>22</v>
       </c>
       <c r="L850" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
       <c r="M850" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
     </row>
     <row r="851">
@@ -37300,10 +37303,10 @@
         <v>22</v>
       </c>
       <c r="L851" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
       <c r="M851" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
     </row>
     <row r="852">
@@ -37341,10 +37344,10 @@
         <v>22</v>
       </c>
       <c r="L852" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
       <c r="M852" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
     </row>
     <row r="853">
@@ -37382,10 +37385,10 @@
         <v>22</v>
       </c>
       <c r="L853" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
       <c r="M853" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
     </row>
     <row r="854">
@@ -37423,10 +37426,10 @@
         <v>22</v>
       </c>
       <c r="L854" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
       <c r="M854" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
     </row>
     <row r="855">
@@ -37464,10 +37467,10 @@
         <v>22</v>
       </c>
       <c r="L855" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
       <c r="M855" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
     </row>
     <row r="856">
@@ -37505,10 +37508,10 @@
         <v>22</v>
       </c>
       <c r="L856" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
       <c r="M856" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
     </row>
     <row r="857">
@@ -37546,10 +37549,10 @@
         <v>22</v>
       </c>
       <c r="L857" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
       <c r="M857" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
     </row>
     <row r="858">
@@ -37587,10 +37590,10 @@
         <v>22</v>
       </c>
       <c r="L858" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
       <c r="M858" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
     </row>
     <row r="859">
@@ -37628,10 +37631,10 @@
         <v>22</v>
       </c>
       <c r="L859" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
       <c r="M859" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
     </row>
     <row r="860">
@@ -37669,10 +37672,10 @@
         <v>22</v>
       </c>
       <c r="L860" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
       <c r="M860" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
     </row>
     <row r="861">
@@ -37710,10 +37713,10 @@
         <v>22</v>
       </c>
       <c r="L861" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
       <c r="M861" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
     </row>
     <row r="862">
@@ -37751,10 +37754,10 @@
         <v>22</v>
       </c>
       <c r="L862" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
       <c r="M862" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
     </row>
     <row r="863">
@@ -37792,10 +37795,10 @@
         <v>22</v>
       </c>
       <c r="L863" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
       <c r="M863" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
     </row>
     <row r="864">
@@ -37833,10 +37836,10 @@
         <v>22</v>
       </c>
       <c r="L864" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
       <c r="M864" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
     </row>
     <row r="865">
@@ -37874,10 +37877,10 @@
         <v>22</v>
       </c>
       <c r="L865" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
       <c r="M865" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
     </row>
     <row r="866">
@@ -37915,10 +37918,10 @@
         <v>22</v>
       </c>
       <c r="L866" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
       <c r="M866" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
     </row>
     <row r="867">
@@ -37956,10 +37959,10 @@
         <v>22</v>
       </c>
       <c r="L867" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
       <c r="M867" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
     </row>
     <row r="868">
@@ -37997,10 +38000,10 @@
         <v>22</v>
       </c>
       <c r="L868" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
       <c r="M868" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
     </row>
     <row r="869">
@@ -38038,10 +38041,10 @@
         <v>22</v>
       </c>
       <c r="L869" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
       <c r="M869" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
     </row>
     <row r="870">
@@ -38079,10 +38082,10 @@
         <v>22</v>
       </c>
       <c r="L870" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
       <c r="M870" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
     </row>
     <row r="871">
@@ -38120,10 +38123,10 @@
         <v>22</v>
       </c>
       <c r="L871" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
       <c r="M871" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
     </row>
     <row r="872">
@@ -38161,10 +38164,10 @@
         <v>22</v>
       </c>
       <c r="L872" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
       <c r="M872" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
     </row>
     <row r="873">
@@ -38202,10 +38205,10 @@
         <v>22</v>
       </c>
       <c r="L873" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
       <c r="M873" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
     </row>
     <row r="874">
@@ -38243,10 +38246,10 @@
         <v>22</v>
       </c>
       <c r="L874" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
       <c r="M874" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
     </row>
     <row r="875">
@@ -38284,10 +38287,10 @@
         <v>22</v>
       </c>
       <c r="L875" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
       <c r="M875" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
     </row>
     <row r="876">
@@ -38325,10 +38328,10 @@
         <v>22</v>
       </c>
       <c r="L876" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
       <c r="M876" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
     </row>
     <row r="877">
@@ -38366,10 +38369,10 @@
         <v>22</v>
       </c>
       <c r="L877" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
       <c r="M877" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
     </row>
     <row r="878">
@@ -38407,10 +38410,10 @@
         <v>22</v>
       </c>
       <c r="L878" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
       <c r="M878" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
     </row>
     <row r="879">
@@ -38448,10 +38451,10 @@
         <v>22</v>
       </c>
       <c r="L879" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
       <c r="M879" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
     </row>
     <row r="880">
@@ -38489,10 +38492,10 @@
         <v>22</v>
       </c>
       <c r="L880" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
       <c r="M880" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
     </row>
     <row r="881">
@@ -38530,10 +38533,10 @@
         <v>22</v>
       </c>
       <c r="L881" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
       <c r="M881" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
     </row>
     <row r="882">
@@ -38571,10 +38574,10 @@
         <v>22</v>
       </c>
       <c r="L882" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
       <c r="M882" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
     </row>
     <row r="883">
@@ -38612,10 +38615,10 @@
         <v>22</v>
       </c>
       <c r="L883" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
       <c r="M883" s="0" t="s">
-        <v>21</v>
+        <v>778</v>
       </c>
     </row>
   </sheetData>
